--- a/AAII_Financials/Yearly/EBON_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/EBON_YR_FIN.xlsx
@@ -1900,10 +1900,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E43" s="3">
-        <v>1600</v>
+        <v>4800</v>
       </c>
       <c r="F43" s="3">
         <v>900</v>
@@ -1978,10 +1978,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="E45" s="3">
-        <v>9300</v>
+        <v>6100</v>
       </c>
       <c r="F45" s="3">
         <v>6200</v>
